--- a/data-manipulation-scripts/sheets-cleanup/sheets/PNEUS 12_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/PNEUS 12_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="58">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -40,7 +40,7 @@
     <t>7897046740822</t>
   </si>
   <si>
-    <t>PNEU VIPAL TR300 17110/90 920701</t>
+    <t>PNEU VIPAL TR300 17 110/90 920701</t>
   </si>
   <si>
     <t>7898576446178</t>
@@ -70,7 +70,7 @@
     <t>602883166707</t>
   </si>
   <si>
-    <t>PNEU 17 60/100</t>
+    <t>PNEU CINBORG 17 60/100</t>
   </si>
   <si>
     <t>7897046740792</t>
@@ -112,19 +112,19 @@
     <t>7898153873830</t>
   </si>
   <si>
-    <t>PNEU MAGGION 14 80/100 USO CAMARA</t>
+    <t>PNEU VIPAL ST600 18 80/100 920323</t>
   </si>
   <si>
     <t xml:space="preserve">  7897046740730</t>
   </si>
   <si>
-    <t>PNEU VIPAL ST600 80/100 920323</t>
+    <t>PNEU VIPAL ST300 18 80/100 920005</t>
   </si>
   <si>
     <t>7897046740921</t>
   </si>
   <si>
-    <t>PNEU VIPAL TR40017 110/90</t>
+    <t>PNEU VIPAL TR400 17 110/90</t>
   </si>
   <si>
     <t>7897046740716</t>
@@ -154,7 +154,10 @@
     <t>3528702759370</t>
   </si>
   <si>
-    <t>PNEU LEVIRIM MATRIX 19 90/90</t>
+    <t>PNEU LEVORIM MATRIX 19 90/90</t>
+  </si>
+  <si>
+    <t>7898153873984</t>
   </si>
   <si>
     <t>PNEU MAGGION 18 90/90</t>
@@ -179,6 +182,9 @@
   </si>
   <si>
     <t>PNEU PROTYRE 18 90/90 TRASEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -498,7 +504,9 @@
       <c r="C3" s="2">
         <v>8.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>275.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -510,7 +518,9 @@
       <c r="C4" s="2">
         <v>4.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>385.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -522,7 +532,9 @@
       <c r="C5" s="2">
         <v>1.0</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>240.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -534,7 +546,9 @@
       <c r="C6" s="2">
         <v>7.0</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="2">
+        <v>290.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -546,7 +560,9 @@
       <c r="C7" s="2">
         <v>4.0</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2">
+        <v>230.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -568,9 +584,11 @@
         <v>19</v>
       </c>
       <c r="C9" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D9" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>170.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -582,7 +600,9 @@
       <c r="C10" s="2">
         <v>3.0</v>
       </c>
-      <c r="D10" s="3"/>
+      <c r="D10" s="2">
+        <v>195.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -594,7 +614,9 @@
       <c r="C11" s="2">
         <v>2.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2">
+        <v>375.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -634,7 +656,9 @@
       <c r="C14" s="2">
         <v>1.0</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="2">
+        <v>190.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -656,151 +680,169 @@
         <v>33</v>
       </c>
       <c r="C16" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D16" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>275.0</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="4"/>
+      <c r="A17" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" s="2">
         <v>1.0</v>
       </c>
-      <c r="D17" s="3"/>
+      <c r="D17" s="2">
+        <v>230.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2">
         <v>1.0</v>
       </c>
-      <c r="D18" s="3"/>
+      <c r="D18" s="2">
+        <v>355.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2">
         <v>1.0</v>
       </c>
-      <c r="D19" s="3"/>
+      <c r="D19" s="2">
+        <v>550.0</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A20" s="4"/>
       <c r="B20" s="2" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
-      <c r="D20" s="3"/>
+      <c r="D20" s="2">
+        <v>240.0</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="4"/>
+      <c r="A21" s="1" t="s">
+        <v>40</v>
+      </c>
       <c r="B21" s="2" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
       <c r="D21" s="2">
-        <v>240.0</v>
+        <v>550.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D22" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="D22" s="2">
+        <v>350.0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D23" s="2">
-        <v>350.0</v>
+        <v>310.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="D24" s="2">
-        <v>310.0</v>
+        <v>290.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2">
         <v>1.0</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="2">
+        <v>270.0</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4"/>
+      <c r="A26" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C26" s="2">
         <v>1.0</v>
       </c>
-      <c r="D26" s="2">
-        <v>270.0</v>
-      </c>
+      <c r="D26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A27" s="4"/>
       <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C27" s="2">
         <v>1.0</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="2">
+        <v>530.0</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="4"/>
+      <c r="A28" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="B28" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C28" s="2">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="D28" s="2">
         <v>530.0</v>
@@ -808,25 +850,27 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C29" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D29" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="D29" s="2">
+        <v>165.0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>55</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="D30" s="2">
+        <v>240.0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4"/>
@@ -6642,20 +6686,14 @@
       <c r="C999" s="3"/>
       <c r="D999" s="3"/>
     </row>
-    <row r="1000">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1000">
+  <conditionalFormatting sqref="A1:A999">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A1000">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A999">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
